--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Tomé</t>
   </si>
   <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabrero</t>
   </si>
   <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Santa Juana</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:20</t>
+    <t xml:space="preserve">2026-09-09 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -829,7 +829,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8303</v>
+        <v>8107</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
@@ -846,7 +846,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8107</v>
+        <v>8303</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:16</t>
+    <t xml:space="preserve">2026-09-17 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:12</t>
+    <t xml:space="preserve">2026-09-23 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:40</t>
+    <t xml:space="preserve">2026-10-02 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Coronel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Cañete</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:08</t>
+    <t xml:space="preserve">2026-10-04 09:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:09</t>
+    <t xml:space="preserve">2026-10-05 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
